--- a/study_case_model/scenario_variables/other_experiment_data/demand_scenarios182.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/demand_scenarios182.xlsx
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>37127.83693391261</v>
+        <v>28877.70733618568</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19221.81400646591</v>
+        <v>31439.13602577534</v>
       </c>
     </row>
     <row r="6">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16787.60573827185</v>
+        <v>13105.20143612941</v>
       </c>
     </row>
     <row r="9">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21109.15192436219</v>
+        <v>18475.24506085938</v>
       </c>
     </row>
     <row r="12">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5277.287981090547</v>
+        <v>4618.811265214845</v>
       </c>
     </row>
     <row r="14">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53782.9228135143</v>
+        <v>41777.55681589776</v>
       </c>
     </row>
     <row r="15">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5111.342819932246</v>
+        <v>9997.588979483906</v>
       </c>
     </row>
     <row r="18">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8478.149850957112</v>
+        <v>12961.22168168851</v>
       </c>
     </row>
     <row r="21">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>23345.75544799515</v>
+        <v>18160.45039891252</v>
       </c>
     </row>
     <row r="24">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>13425.89773781229</v>
+        <v>8971.799264066822</v>
       </c>
     </row>
     <row r="27">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>13248.81303357366</v>
+        <v>16955.92882409578</v>
       </c>
     </row>
     <row r="30">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3312.203258393416</v>
+        <v>4238.982206023946</v>
       </c>
     </row>
     <row r="32">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>33669.59884285487</v>
+        <v>73433.66315957437</v>
       </c>
     </row>
     <row r="33">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>14605.522361848</v>
+        <v>11909.14266667334</v>
       </c>
     </row>
     <row r="36">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>29221.40860342848</v>
+        <v>26813.25167413233</v>
       </c>
     </row>
     <row r="39">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>23966.94204709055</v>
+        <v>27049.89733383945</v>
       </c>
     </row>
     <row r="42">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>15425.75645444778</v>
+        <v>18453.42842315888</v>
       </c>
     </row>
     <row r="45">
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>12954.78622567912</v>
+        <v>16546.48727692825</v>
       </c>
     </row>
     <row r="48">
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3238.69655641978</v>
+        <v>4136.621819232062</v>
       </c>
     </row>
     <row r="50">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>44660.97624369544</v>
+        <v>46662.16879612908</v>
       </c>
     </row>
     <row r="51">
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>18679.54102168878</v>
+        <v>12101.75235584681</v>
       </c>
     </row>
     <row r="54">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>25512.41597454863</v>
+        <v>33524.01141831077</v>
       </c>
     </row>
     <row r="57">
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>25947.3438594025</v>
+        <v>35080.79270315841</v>
       </c>
     </row>
     <row r="60">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>21147.29969737903</v>
+        <v>14279.68932385229</v>
       </c>
     </row>
     <row r="63">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>11603.94700490738</v>
+        <v>27397.45624437128</v>
       </c>
     </row>
     <row r="66">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2900.986751226844</v>
+        <v>6849.36406109282</v>
       </c>
     </row>
     <row r="68">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>61946.45549963166</v>
+        <v>52664.91494703483</v>
       </c>
     </row>
     <row r="69">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>18739.94854928037</v>
+        <v>11852.73782143692</v>
       </c>
     </row>
     <row r="72">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>22563.5655512609</v>
+        <v>33840.43064939216</v>
       </c>
     </row>
     <row r="75">
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>31447.23090141135</v>
+        <v>28657.13256425348</v>
       </c>
     </row>
     <row r="78">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>8817.426885459106</v>
+        <v>9741.760002846568</v>
       </c>
     </row>
     <row r="81">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>15879.60562659589</v>
+        <v>25984.52562874611</v>
       </c>
     </row>
     <row r="84">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3969.901406648973</v>
+        <v>6496.131407186527</v>
       </c>
     </row>
     <row r="86">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>55774.49624071451</v>
+        <v>46872.61053469581</v>
       </c>
     </row>
     <row r="87">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>15494.62502416471</v>
+        <v>11259.41178978423</v>
       </c>
     </row>
     <row r="90">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>33407.02384304685</v>
+        <v>31697.53276149784</v>
       </c>
     </row>
     <row r="93">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>36772.2144020462</v>
+        <v>24333.75894366315</v>
       </c>
     </row>
     <row r="96">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>12247.07540541807</v>
+        <v>13958.59451015109</v>
       </c>
     </row>
     <row r="99">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>27161.67053103553</v>
+        <v>23971.6375044248</v>
       </c>
     </row>
     <row r="102">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6790.417632758883</v>
+        <v>5992.909376106199</v>
       </c>
     </row>
     <row r="104">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>44865.42734826277</v>
+        <v>38255.85381091424</v>
       </c>
     </row>
     <row r="105">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>15882.84241845601</v>
+        <v>13943.18961755826</v>
       </c>
     </row>
     <row r="108">
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>26556.16598389136</v>
+        <v>35121.04828946217</v>
       </c>
     </row>
     <row r="111">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>28342.58430311442</v>
+        <v>17826.49642195292</v>
       </c>
     </row>
     <row r="114">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>14088.15452758264</v>
+        <v>14187.1583331171</v>
       </c>
     </row>
     <row r="117">
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>10371.76994121313</v>
+        <v>15023.19359251828</v>
       </c>
     </row>
     <row r="120">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2592.942485303282</v>
+        <v>3755.798398129569</v>
       </c>
     </row>
     <row r="122">
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>33138.1721170884</v>
+        <v>65320.96525760598</v>
       </c>
     </row>
     <row r="123">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>12884.53039931571</v>
+        <v>16294.64593906164</v>
       </c>
     </row>
     <row r="126">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>12345.40690269124</v>
+        <v>22342.58244813176</v>
       </c>
     </row>
     <row r="129">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>31234.08327399817</v>
+        <v>41572.21489143147</v>
       </c>
     </row>
     <row r="132">
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>15768.33487358053</v>
+        <v>16649.84490926482</v>
       </c>
     </row>
     <row r="135">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>21963.02331726675</v>
+        <v>24241.57391081702</v>
       </c>
     </row>
     <row r="138">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5490.755829316687</v>
+        <v>6060.393477704254</v>
       </c>
     </row>
     <row r="140">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>33182.98980863117</v>
+        <v>59759.16344159203</v>
       </c>
     </row>
     <row r="141">
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>17675.52102075693</v>
+        <v>16189.72590952334</v>
       </c>
     </row>
     <row r="144">
